--- a/data/trans_orig/P36B11-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B11-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2007</t>
+          <t>Población según la frecuencia de consumo de pescado en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51667</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44143</t>
+          <t>45765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74551</t>
+          <t>75987</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>196340</t>
+          <t>198689</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>241056</t>
+          <t>243289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>151470</t>
+          <t>151671</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>184917</t>
+          <t>185747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>361697</t>
+          <t>358795</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>415561</t>
+          <t>415913</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170950</t>
+          <t>171614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215044</t>
+          <t>214073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89806</t>
+          <t>89977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121757</t>
+          <t>121107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273513</t>
+          <t>271595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326975</t>
+          <t>327533</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,97%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>34495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41838</t>
+          <t>40928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43821</t>
+          <t>43565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72116</t>
+          <t>71571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>192064</t>
+          <t>191599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>230462</t>
+          <t>229645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201874</t>
+          <t>203069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>239541</t>
+          <t>240154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>404668</t>
+          <t>405012</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>457921</t>
+          <t>458092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94720</t>
+          <t>96671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131674</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85617</t>
+          <t>85369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122844</t>
+          <t>120293</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190971</t>
+          <t>190252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239402</t>
+          <t>241056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22830</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>43341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70111</t>
+          <t>70826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17530</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50584</t>
+          <t>51113</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82037</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>243227</t>
+          <t>243546</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>290838</t>
+          <t>289108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76590</t>
+          <t>78126</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102978</t>
+          <t>103140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>331216</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>382206</t>
+          <t>383382</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>176207</t>
+          <t>175946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>221451</t>
+          <t>221950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48441</t>
+          <t>47866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72737</t>
+          <t>73112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>236395</t>
+          <t>234207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>284848</t>
+          <t>287008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>804</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19806</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27425</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>22827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43421</t>
+          <t>44391</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69514</t>
+          <t>69893</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103317</t>
+          <t>103657</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>49802</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>79253</t>
+          <t>78210</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127347</t>
+          <t>125819</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>171472</t>
+          <t>173721</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>596276</t>
+          <t>593812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>665384</t>
+          <t>668238</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>349127</t>
+          <t>349796</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>402151</t>
+          <t>403188</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>964010</t>
+          <t>963767</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1051891</t>
+          <t>1052279</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>441974</t>
+          <t>443942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>508408</t>
+          <t>512689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>222163</t>
+          <t>218900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>273759</t>
+          <t>272029</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>679641</t>
+          <t>675944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>765361</t>
+          <t>764944</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>41386</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23701</t>
+          <t>24108</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57723</t>
+          <t>57370</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14933</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35359</t>
+          <t>35411</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23871</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>47182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>25381</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53423</t>
+          <t>51052</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>57755</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93186</t>
+          <t>91214</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>133743</t>
+          <t>134700</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>172700</t>
+          <t>172944</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>268044</t>
+          <t>264724</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>315152</t>
+          <t>315705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>411274</t>
+          <t>413401</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>472157</t>
+          <t>474075</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>124545</t>
+          <t>126135</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>163341</t>
+          <t>164336</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>182887</t>
+          <t>182621</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>226991</t>
+          <t>230980</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>323028</t>
+          <t>317440</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>378810</t>
+          <t>379857</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28483</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40199</t>
+          <t>41269</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>58029</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69810</t>
+          <t>70368</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>104644</t>
+          <t>106279</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>108723</t>
+          <t>111296</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>150950</t>
+          <t>154880</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>126480</t>
+          <t>126491</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>160524</t>
+          <t>159112</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>653141</t>
+          <t>651547</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>721088</t>
+          <t>720219</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>793069</t>
+          <t>789370</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>868345</t>
+          <t>866829</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>91655</t>
+          <t>90399</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>122632</t>
+          <t>122786</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>402630</t>
+          <t>402353</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>466981</t>
+          <t>465869</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>503500</t>
+          <t>503281</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>577119</t>
+          <t>579646</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17577</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>41056</t>
+          <t>38443</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>42586</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>39396</t>
+          <t>37708</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>68354</t>
+          <t>67141</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>78801</t>
+          <t>76723</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>92502</t>
+          <t>92158</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>135947</t>
+          <t>135457</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>255368</t>
+          <t>257059</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>320903</t>
+          <t>318649</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>216512</t>
+          <t>216653</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>276140</t>
+          <t>276032</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>488413</t>
+          <t>486560</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>580900</t>
+          <t>575678</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1567728</t>
+          <t>1572215</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1684610</t>
+          <t>1680782</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1775603</t>
+          <t>1774198</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1893476</t>
+          <t>1889322</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3368694</t>
+          <t>3370268</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3542271</t>
+          <t>3543418</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1176324</t>
+          <t>1176380</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1293716</t>
+          <t>1284025</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1097180</t>
+          <t>1099139</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1206915</t>
+          <t>1209902</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2308283</t>
+          <t>2312766</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2469845</t>
+          <t>2469724</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>59042</t>
+          <t>58837</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>94498</t>
+          <t>96376</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>65437</t>
+          <t>65511</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>102302</t>
+          <t>101593</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>135869</t>
+          <t>132575</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>183404</t>
+          <t>183837</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2012</t>
+          <t>Población según la frecuencia de consumo de pescado en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37683</t>
+          <t>37498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29972</t>
+          <t>28281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>31859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59269</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199279</t>
+          <t>199858</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244734</t>
+          <t>244381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130138</t>
+          <t>133224</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168221</t>
+          <t>169234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>344462</t>
+          <t>343532</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>404725</t>
+          <t>403004</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150116</t>
+          <t>150213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195374</t>
+          <t>193093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111015</t>
+          <t>110869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147089</t>
+          <t>147480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>271615</t>
+          <t>268408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328496</t>
+          <t>325774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21288</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21758</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37614</t>
+          <t>37684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>13245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>32419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42004</t>
+          <t>41902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41771</t>
+          <t>40303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44766</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73486</t>
+          <t>75265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189211</t>
+          <t>191036</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>236825</t>
+          <t>234762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142643</t>
+          <t>144755</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184164</t>
+          <t>184289</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>347299</t>
+          <t>344224</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>404635</t>
+          <t>404443</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132266</t>
+          <t>134239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176190</t>
+          <t>176109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108805</t>
+          <t>108657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147615</t>
+          <t>147089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257336</t>
+          <t>258136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313355</t>
+          <t>316509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19183</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>27015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20140</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42950</t>
+          <t>44337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74119</t>
+          <t>75713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27736</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60248</t>
+          <t>58537</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94481</t>
+          <t>94444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>297136</t>
+          <t>294213</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>349992</t>
+          <t>346370</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124897</t>
+          <t>124608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158664</t>
+          <t>156562</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>433440</t>
+          <t>428172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>492589</t>
+          <t>491555</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>193054</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>242119</t>
+          <t>243719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80217</t>
+          <t>81355</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112778</t>
+          <t>112821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284048</t>
+          <t>283837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341565</t>
+          <t>342746</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21993</t>
+          <t>22832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>34061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110251</t>
+          <t>108384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>155825</t>
+          <t>151455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45767</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78081</t>
+          <t>76984</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>165073</t>
+          <t>164328</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217621</t>
+          <t>218763</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>563223</t>
+          <t>563563</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>633406</t>
+          <t>634393</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>369744</t>
+          <t>373025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>427240</t>
+          <t>432256</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>958626</t>
+          <t>950171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1042768</t>
+          <t>1042601</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>354400</t>
+          <t>353297</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>417417</t>
+          <t>419561</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>238832</t>
+          <t>236675</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>295465</t>
+          <t>294413</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>609035</t>
+          <t>611839</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>691127</t>
+          <t>690958</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>22809</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47466</t>
+          <t>46998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33698</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40962</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>74377</t>
+          <t>71290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>67004</t>
+          <t>65322</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68585</t>
+          <t>69019</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>84984</t>
+          <t>85371</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>124583</t>
+          <t>124346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>246784</t>
+          <t>247173</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>294037</t>
+          <t>293450</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>366663</t>
+          <t>364722</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>423432</t>
+          <t>423857</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>628437</t>
+          <t>627372</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>698140</t>
+          <t>697447</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>145774</t>
+          <t>146656</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>191125</t>
+          <t>189812</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>248556</t>
+          <t>249848</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>303425</t>
+          <t>304420</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>409016</t>
+          <t>410683</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>479939</t>
+          <t>477353</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28230</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>41814</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>62006</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13762</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27116</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>22158</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44241</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>63765</t>
+          <t>64995</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>100621</t>
+          <t>99881</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>95753</t>
+          <t>94790</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>134925</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>138181</t>
+          <t>138172</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>169406</t>
+          <t>169377</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>564663</t>
+          <t>565520</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>629783</t>
+          <t>630797</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>715146</t>
+          <t>717103</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>791137</t>
+          <t>792675</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>55186</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>82180</t>
+          <t>82541</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>360891</t>
+          <t>360719</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>424084</t>
+          <t>422736</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>424381</t>
+          <t>422364</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>495758</t>
+          <t>495440</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>30622</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37475</t>
+          <t>35886</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>36111</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>67085</t>
+          <t>66724</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34380</t>
+          <t>34454</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>62805</t>
+          <t>60351</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>75484</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>116252</t>
+          <t>117049</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>290824</t>
+          <t>289448</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>366036</t>
+          <t>363783</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>230651</t>
+          <t>231198</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>293818</t>
+          <t>293121</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>540559</t>
+          <t>540156</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>635043</t>
+          <t>633833</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1721478</t>
+          <t>1727213</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1836468</t>
+          <t>1845371</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1785440</t>
+          <t>1789261</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1913194</t>
+          <t>1913104</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3556085</t>
+          <t>3536919</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3717561</t>
+          <t>3703003</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1113119</t>
+          <t>1106995</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1219529</t>
+          <t>1221658</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1221342</t>
+          <t>1225996</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1338149</t>
+          <t>1345087</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2366109</t>
+          <t>2375973</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2526970</t>
+          <t>2532271</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>75786</t>
+          <t>75900</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>114996</t>
+          <t>116800</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>81465</t>
+          <t>82909</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>123012</t>
+          <t>123600</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>168191</t>
+          <t>165911</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>226202</t>
+          <t>225983</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2016</t>
+          <t>Población según la frecuencia de consumo de pescado en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41648</t>
+          <t>41045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37064</t>
+          <t>36347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41283</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70669</t>
+          <t>70196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>241290</t>
+          <t>244802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>286107</t>
+          <t>284984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>204508</t>
+          <t>203448</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>242040</t>
+          <t>240750</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>459128</t>
+          <t>458935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>513343</t>
+          <t>517098</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102760</t>
+          <t>102810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141993</t>
+          <t>138847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77076</t>
+          <t>76731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109540</t>
+          <t>111184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191055</t>
+          <t>189877</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241763</t>
+          <t>236418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>23018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20104</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44521</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49941</t>
+          <t>52124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54076</t>
+          <t>53572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86644</t>
+          <t>85567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210890</t>
+          <t>211103</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>249237</t>
+          <t>249444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>203100</t>
+          <t>204139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>242347</t>
+          <t>242999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>429659</t>
+          <t>430199</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>483796</t>
+          <t>484184</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93139</t>
+          <t>92325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130442</t>
+          <t>128807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115673</t>
+          <t>113872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181537</t>
+          <t>181503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231543</t>
+          <t>231703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,47 +11917,47 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9779</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>3948</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10057</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3948</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>24268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37036</t>
+          <t>37974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64996</t>
+          <t>66415</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47510</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77906</t>
+          <t>78622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>291492</t>
+          <t>293296</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>335171</t>
+          <t>336230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86553</t>
+          <t>88292</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112139</t>
+          <t>114183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>389616</t>
+          <t>390166</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>440255</t>
+          <t>441398</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120819</t>
+          <t>122131</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162371</t>
+          <t>162416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37564</t>
+          <t>36788</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60735</t>
+          <t>61797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166453</t>
+          <t>168411</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>214796</t>
+          <t>214945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41070</t>
+          <t>40211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>89936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131753</t>
+          <t>131041</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57079</t>
+          <t>56552</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88854</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>154696</t>
+          <t>157285</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>206603</t>
+          <t>209332</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>641079</t>
+          <t>640490</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>709492</t>
+          <t>706561</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>447964</t>
+          <t>448072</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>506744</t>
+          <t>507414</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1109463</t>
+          <t>1110552</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1199155</t>
+          <t>1199239</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>299574</t>
+          <t>302706</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>361508</t>
+          <t>362793</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>218702</t>
+          <t>218312</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>272270</t>
+          <t>273210</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>535585</t>
+          <t>537856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>620749</t>
+          <t>617362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27932</t>
+          <t>28353</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20620</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44063</t>
+          <t>42329</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>55689</t>
+          <t>58033</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>90143</t>
+          <t>91582</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>50042</t>
+          <t>51526</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82967</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>116465</t>
+          <t>115451</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>161498</t>
+          <t>162602</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>358280</t>
+          <t>358572</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>407828</t>
+          <t>408089</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>420118</t>
+          <t>420103</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>477610</t>
+          <t>476330</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>792943</t>
+          <t>794653</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>869282</t>
+          <t>869776</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>118970</t>
+          <t>120135</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>161333</t>
+          <t>162159</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>171708</t>
+          <t>173892</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>225328</t>
+          <t>223266</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>306744</t>
+          <t>306623</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>372576</t>
+          <t>369720</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33352</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>45404</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>75031</t>
+          <t>74147</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>110890</t>
+          <t>112179</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>108196</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>151584</t>
+          <t>149872</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>164853</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>197702</t>
+          <t>197058</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>606876</t>
+          <t>603950</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>668918</t>
+          <t>670120</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>782907</t>
+          <t>781830</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>854446</t>
+          <t>854699</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>50040</t>
+          <t>51301</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>79220</t>
+          <t>79625</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>280005</t>
+          <t>280728</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>338897</t>
+          <t>336916</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>338431</t>
+          <t>337006</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>406001</t>
+          <t>406812</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>35697</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40391</t>
+          <t>40341</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>40159</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>71269</t>
+          <t>70183</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>41581</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>70449</t>
+          <t>70441</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>87392</t>
+          <t>88809</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>130249</t>
+          <t>132729</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>290515</t>
+          <t>293786</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>361244</t>
+          <t>366552</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>272753</t>
+          <t>271905</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>337798</t>
+          <t>337948</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>583841</t>
+          <t>586736</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>679843</t>
+          <t>681888</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1992693</t>
+          <t>1989349</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2104143</t>
+          <t>2105735</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2052943</t>
+          <t>2047973</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2177165</t>
+          <t>2167834</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4078210</t>
+          <t>4078827</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4241089</t>
+          <t>4246283</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>857279</t>
+          <t>855102</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>961379</t>
+          <t>963446</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>933575</t>
+          <t>939100</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1043576</t>
+          <t>1042148</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1823122</t>
+          <t>1818999</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1970654</t>
+          <t>1978332</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>29008</t>
+          <t>28489</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>55933</t>
+          <t>56306</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>48849</t>
+          <t>48370</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>81244</t>
+          <t>79408</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>85368</t>
+          <t>82509</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>126336</t>
+          <t>124618</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B11-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B11-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27576</t>
+          <t>27362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51030</t>
+          <t>52862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>29630</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45765</t>
+          <t>42826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75987</t>
+          <t>75502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>198689</t>
+          <t>197895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243289</t>
+          <t>241839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>151671</t>
+          <t>149818</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>185747</t>
+          <t>185453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>358795</t>
+          <t>357758</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>415913</t>
+          <t>415029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171614</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214073</t>
+          <t>215241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89977</t>
+          <t>88949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121107</t>
+          <t>122278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>271595</t>
+          <t>273178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327533</t>
+          <t>327760</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>25539</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34495</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,47 +1464,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>13427</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>7703</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>22379</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13427</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>22112</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>38550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>19623</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40928</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43565</t>
+          <t>44488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71571</t>
+          <t>71542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>191599</t>
+          <t>188927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>229645</t>
+          <t>229697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>203069</t>
+          <t>201389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>240154</t>
+          <t>238649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>405012</t>
+          <t>405814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>458092</t>
+          <t>457750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96671</t>
+          <t>94993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132977</t>
+          <t>132259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85369</t>
+          <t>86443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120293</t>
+          <t>121183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190252</t>
+          <t>191641</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241056</t>
+          <t>240652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31230</t>
+          <t>31181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22396</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43341</t>
+          <t>43409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70826</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>51313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82011</t>
+          <t>81604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>243546</t>
+          <t>239263</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>289108</t>
+          <t>287207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78126</t>
+          <t>76583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103140</t>
+          <t>101945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>327797</t>
+          <t>329232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>383382</t>
+          <t>380729</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>175946</t>
+          <t>176204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>221950</t>
+          <t>222163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47866</t>
+          <t>49115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73112</t>
+          <t>74634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>234207</t>
+          <t>237777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>287008</t>
+          <t>286570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27750</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>20916</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44391</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69893</t>
+          <t>69055</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103657</t>
+          <t>104744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49802</t>
+          <t>49560</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78210</t>
+          <t>79943</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125819</t>
+          <t>125768</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>173721</t>
+          <t>173222</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>593812</t>
+          <t>595248</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>668238</t>
+          <t>669667</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>349796</t>
+          <t>348273</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>403188</t>
+          <t>401569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>963767</t>
+          <t>963865</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1052279</t>
+          <t>1052652</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>443942</t>
+          <t>437482</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>512689</t>
+          <t>511844</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>218900</t>
+          <t>220496</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>272029</t>
+          <t>269765</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>675944</t>
+          <t>679985</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>764944</t>
+          <t>763312</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41386</t>
+          <t>39449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31142</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57370</t>
+          <t>57757</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35411</t>
+          <t>37586</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25323</t>
+          <t>25423</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47182</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25381</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>51052</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56208</t>
+          <t>56308</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>91214</t>
+          <t>89041</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>134700</t>
+          <t>134561</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>172944</t>
+          <t>173285</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>264724</t>
+          <t>264779</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>315705</t>
+          <t>312991</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>413401</t>
+          <t>413688</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>474075</t>
+          <t>473792</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>126135</t>
+          <t>125647</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>164336</t>
+          <t>165056</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>182621</t>
+          <t>184511</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>230980</t>
+          <t>228225</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>317440</t>
+          <t>320907</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>379857</t>
+          <t>380371</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>28653</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20047</t>
+          <t>20341</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>41269</t>
+          <t>40808</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>835</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>21672</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>56615</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>70368</t>
+          <t>69234</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>106279</t>
+          <t>104452</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>109725</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>154880</t>
+          <t>152369</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>126491</t>
+          <t>125421</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>159112</t>
+          <t>158874</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>651547</t>
+          <t>650055</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>720219</t>
+          <t>719693</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>789370</t>
+          <t>791536</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>866829</t>
+          <t>868780</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>90399</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>122786</t>
+          <t>122672</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>402353</t>
+          <t>404692</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>465869</t>
+          <t>471061</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,47 +4531,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>541158</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>507662</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>577173</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>34,98%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>32,82%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>37,31%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>541158</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>503281</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>579646</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>32,53%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>843</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38443</t>
+          <t>38055</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>41843</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>38946</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>67141</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>45875</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>76723</t>
+          <t>77425</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>92158</t>
+          <t>92630</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>135457</t>
+          <t>133679</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>257059</t>
+          <t>251767</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>318649</t>
+          <t>316344</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>216653</t>
+          <t>216442</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>276032</t>
+          <t>276485</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>486560</t>
+          <t>492586</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>575678</t>
+          <t>579877</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1572215</t>
+          <t>1564846</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1680782</t>
+          <t>1677294</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1774198</t>
+          <t>1776229</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1889322</t>
+          <t>1888593</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3370268</t>
+          <t>3380630</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3543418</t>
+          <t>3538721</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,25%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1176380</t>
+          <t>1178563</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1284025</t>
+          <t>1287658</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1099139</t>
+          <t>1103159</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1209902</t>
+          <t>1210097</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2312766</t>
+          <t>2300779</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2469724</t>
+          <t>2458705</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>58837</t>
+          <t>59877</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>96376</t>
+          <t>94471</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>65511</t>
+          <t>66869</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>101593</t>
+          <t>104588</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>132575</t>
+          <t>136201</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>183837</t>
+          <t>186670</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>929</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37498</t>
+          <t>36545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28281</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>31193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>59489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199858</t>
+          <t>200383</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244381</t>
+          <t>243759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133224</t>
+          <t>130375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169234</t>
+          <t>168811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>343532</t>
+          <t>344049</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>403004</t>
+          <t>401201</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150213</t>
+          <t>152228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193093</t>
+          <t>193861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110869</t>
+          <t>109019</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147480</t>
+          <t>147825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>268408</t>
+          <t>275999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325774</t>
+          <t>329438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>13420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32419</t>
+          <t>32473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>20631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41902</t>
+          <t>43811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40303</t>
+          <t>40866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44219</t>
+          <t>44121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75265</t>
+          <t>76482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>191036</t>
+          <t>192703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>234762</t>
+          <t>236723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144755</t>
+          <t>143760</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184289</t>
+          <t>183727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>344224</t>
+          <t>349426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>404443</t>
+          <t>408913</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134239</t>
+          <t>134620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176109</t>
+          <t>175778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108657</t>
+          <t>108746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147089</t>
+          <t>146873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258136</t>
+          <t>254255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316509</t>
+          <t>312536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44337</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75713</t>
+          <t>74029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,47 +7267,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>75086</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>58459</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>93377</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>10,51%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>75086</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>58537</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>94444</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>294213</t>
+          <t>294278</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>346370</t>
+          <t>348522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124608</t>
+          <t>123266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>156562</t>
+          <t>156510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>428172</t>
+          <t>430408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>491555</t>
+          <t>490331</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>193917</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>243719</t>
+          <t>242703</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81355</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112821</t>
+          <t>112576</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>283837</t>
+          <t>284618</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>342746</t>
+          <t>344096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17891</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>15578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34061</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108384</t>
+          <t>109054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>151455</t>
+          <t>153387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47239</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76984</t>
+          <t>77382</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>164328</t>
+          <t>165235</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218763</t>
+          <t>220487</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>563563</t>
+          <t>562512</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>634393</t>
+          <t>633554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>373025</t>
+          <t>373456</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>432256</t>
+          <t>426750</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>950171</t>
+          <t>949640</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1042601</t>
+          <t>1041589</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>353297</t>
+          <t>351733</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>419561</t>
+          <t>418634</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,82 +8140,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>36,22%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>265405</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>239036</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>292259</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>34,8%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>31,34%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>38,32%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>650726</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>612000</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>696433</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>36,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>265405</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>236675</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>294413</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>34,8%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>650726</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>611839</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>690958</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>33,92%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>31,89%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22809</t>
+          <t>22989</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46998</t>
+          <t>47902</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32485</t>
+          <t>34207</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41618</t>
+          <t>41610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71290</t>
+          <t>72031</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>65322</t>
+          <t>66937</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69019</t>
+          <t>68333</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>85371</t>
+          <t>85113</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>124346</t>
+          <t>123074</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>247173</t>
+          <t>246190</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>293450</t>
+          <t>290724</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>364722</t>
+          <t>368280</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>423857</t>
+          <t>425238</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>627372</t>
+          <t>628274</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>697447</t>
+          <t>699219</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>147624</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>189812</t>
+          <t>190312</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>249848</t>
+          <t>247238</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>304420</t>
+          <t>302934</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>410683</t>
+          <t>409569</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>477353</t>
+          <t>478708</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>26653</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41814</t>
+          <t>42270</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>64106</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>26621</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34992</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22158</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>43040</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>64995</t>
+          <t>64834</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>99881</t>
+          <t>100599</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>94790</t>
+          <t>92611</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>136796</t>
+          <t>133081</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>138172</t>
+          <t>138596</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>169377</t>
+          <t>170179</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>565520</t>
+          <t>564342</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>630797</t>
+          <t>631728</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>717103</t>
+          <t>716968</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>792675</t>
+          <t>790937</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>53186</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>82541</t>
+          <t>81306</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,82 +9504,82 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>30,47%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>392161</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>360795</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>421824</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>35,41%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>38,09%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>460008</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>425105</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>495605</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>30,93%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>392161</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>360719</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>422736</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>35,41%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>38,17%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>460008</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>422364</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>495440</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>30,73%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>31783</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>37301</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>36111</t>
+          <t>36892</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>66724</t>
+          <t>65887</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34454</t>
+          <t>34188</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>60351</t>
+          <t>61734</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>75484</t>
+          <t>76161</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>117049</t>
+          <t>116200</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>289448</t>
+          <t>291380</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>363783</t>
+          <t>363204</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>231198</t>
+          <t>227054</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>293121</t>
+          <t>290906</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>540156</t>
+          <t>536936</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>633833</t>
+          <t>632806</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1727213</t>
+          <t>1714702</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1845371</t>
+          <t>1840189</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1789261</t>
+          <t>1793513</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1913104</t>
+          <t>1918291</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3536919</t>
+          <t>3542819</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3703003</t>
+          <t>3716784</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1106995</t>
+          <t>1107909</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1221658</t>
+          <t>1219190</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1225996</t>
+          <t>1218877</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1345087</t>
+          <t>1341587</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2375973</t>
+          <t>2358102</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2532271</t>
+          <t>2532311</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>75900</t>
+          <t>74997</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>116800</t>
+          <t>116623</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>82909</t>
+          <t>82473</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>123600</t>
+          <t>123173</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>165911</t>
+          <t>168195</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>225983</t>
+          <t>224665</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>15169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>43149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36347</t>
+          <t>37034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41036</t>
+          <t>40040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>69824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>244802</t>
+          <t>241636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>284984</t>
+          <t>285049</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>203448</t>
+          <t>205704</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>240750</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>458935</t>
+          <t>462254</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>517098</t>
+          <t>515706</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102810</t>
+          <t>100986</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138847</t>
+          <t>140281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111184</t>
+          <t>108218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>189877</t>
+          <t>187719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236418</t>
+          <t>238131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23153</t>
+          <t>21534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46084</t>
+          <t>44551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>26493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52124</t>
+          <t>51159</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85567</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211103</t>
+          <t>209413</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>249444</t>
+          <t>248712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>204139</t>
+          <t>204694</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>242999</t>
+          <t>243332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>430199</t>
+          <t>429416</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>484184</t>
+          <t>484257</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92325</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128807</t>
+          <t>128915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80006</t>
+          <t>80990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113872</t>
+          <t>118324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181503</t>
+          <t>182391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231703</t>
+          <t>229849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>24877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>37404</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66415</t>
+          <t>64931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47063</t>
+          <t>48101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78622</t>
+          <t>77710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>293296</t>
+          <t>292026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>336230</t>
+          <t>336659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88292</t>
+          <t>86897</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114183</t>
+          <t>112986</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>390166</t>
+          <t>388386</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441398</t>
+          <t>441807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,21%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>122131</t>
+          <t>119834</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162416</t>
+          <t>162318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36788</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>60222</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168411</t>
+          <t>167152</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>214945</t>
+          <t>214302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>10764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18470</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40211</t>
+          <t>41551</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89936</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131041</t>
+          <t>132228</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56552</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>88611</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>157285</t>
+          <t>155317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>209332</t>
+          <t>205339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>640490</t>
+          <t>640045</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>706561</t>
+          <t>708179</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>448072</t>
+          <t>450865</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>507414</t>
+          <t>509336</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1110552</t>
+          <t>1106820</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1199239</t>
+          <t>1197444</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>302706</t>
+          <t>297384</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>362793</t>
+          <t>362599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>218312</t>
+          <t>215659</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>273210</t>
+          <t>271052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>537856</t>
+          <t>537393</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>617362</t>
+          <t>620910</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28353</t>
+          <t>28411</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42329</t>
+          <t>43330</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>24894</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19083</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37305</t>
+          <t>37365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58033</t>
+          <t>57010</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91582</t>
+          <t>90254</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51526</t>
+          <t>50357</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83253</t>
+          <t>81945</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>115451</t>
+          <t>117637</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>162602</t>
+          <t>163375</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>358572</t>
+          <t>357985</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>408089</t>
+          <t>408176</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>420103</t>
+          <t>421975</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>476330</t>
+          <t>477852</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>794653</t>
+          <t>796911</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>869776</t>
+          <t>870327</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>120135</t>
+          <t>119871</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>162159</t>
+          <t>160560</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>173892</t>
+          <t>173498</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>223266</t>
+          <t>222332</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>306623</t>
+          <t>304933</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>369720</t>
+          <t>369311</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33177</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26320</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>31943</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>24038</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>45404</t>
+          <t>46429</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>74147</t>
+          <t>76001</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>112179</t>
+          <t>112221</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>108196</t>
+          <t>106960</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>149872</t>
+          <t>149953</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>164853</t>
+          <t>164423</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>197058</t>
+          <t>196550</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>603950</t>
+          <t>604816</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>670120</t>
+          <t>671106</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>781830</t>
+          <t>780317</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>854699</t>
+          <t>856462</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>51301</t>
+          <t>52011</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>79625</t>
+          <t>78519</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>280728</t>
+          <t>279172</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>336916</t>
+          <t>340796</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>337006</t>
+          <t>338817</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>406812</t>
+          <t>407183</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9757</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40341</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>40159</t>
+          <t>40565</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>70183</t>
+          <t>70856</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>40428</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>70441</t>
+          <t>70687</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>88809</t>
+          <t>88660</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>132729</t>
+          <t>131189</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>293786</t>
+          <t>294186</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>366552</t>
+          <t>366531</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>271905</t>
+          <t>269853</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>337948</t>
+          <t>341357</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>586736</t>
+          <t>585030</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>681888</t>
+          <t>679266</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1989349</t>
+          <t>1988760</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2105735</t>
+          <t>2106582</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2047973</t>
+          <t>2054924</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2167834</t>
+          <t>2169061</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4078827</t>
+          <t>4079810</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4246283</t>
+          <t>4237359</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>855102</t>
+          <t>855402</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>963446</t>
+          <t>959826</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>939100</t>
+          <t>937771</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1042148</t>
+          <t>1045297</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1818999</t>
+          <t>1822826</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1978332</t>
+          <t>1975552</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>56306</t>
+          <t>56134</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>48370</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>79408</t>
+          <t>80140</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>82509</t>
+          <t>84179</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>124618</t>
+          <t>126817</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
